--- a/output/pms/Lập_trình_Python/Session 04 - Toán tử số học, logic và Cấu trúc rẽ nhánh/Lesson 01 - Toán tử số học và toán tử gán/Câu hỏi Quizz/Quizz_Session04_Lesson01.xlsx
+++ b/output/pms/Lập_trình_Python/Session 04 - Toán tử số học, logic và Cấu trúc rẽ nhánh/Lesson 01 - Toán tử số học và toán tử gán/Câu hỏi Quizz/Quizz_Session04_Lesson01.xlsx
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="65" customWidth="1" min="1" max="1"/>
@@ -483,11 +483,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Cho đoạn mã xử lý biểu thức tính điểm thưởng lũy thừa trong hệ thống như sau:
-```python
-ket_qua = 2 ** 3 ** 2
-```
-Giá trị của biến `ket_qua` sau khi Python thực thi là bao nhiêu?</t>
+          <t>Hệ thống kho của Techmart Enterprise cần xác định chính xác số lượng thùng hàng nguyên vẹn khi đóng gói `items_count` sản phẩm vào các thùng có sức chứa `box_capacity`. Cú pháp nào dưới đây sử dụng đúng toán tử số học trong Python để trả về kết quả dưới dạng số nguyên `int`?</t>
         </is>
       </c>
       <c r="B2" s="3" t="n">
@@ -495,7 +491,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>512 vì toán tử lũy thừa ** có tính kết hợp từ phải sang trái.</t>
+          <t>full_boxes = items_count // box_capacity</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -509,42 +505,35 @@
       <c r="B3" s="4" t="n"/>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>64 vì toán tử lũy thừa ** được thực hiện lần lượt từ trái sang phải.</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr"/>
+          <t>full_boxes = items_count / box_capacity</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n"/>
       <c r="B4" s="4" t="n"/>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>36 vì hệ thống tự động quy đổi thành phép nhân số mũ.</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr"/>
+          <t>full_boxes = items_count % box_capacity</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n"/>
       <c r="B5" s="4" t="n"/>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12 vì hệ thống thực hiện phép nhân các cơ số từ trái qua phải.</t>
-        </is>
-      </c>
-      <c r="D5" s="3" t="inlineStr"/>
+          <t>full_boxes = items_count ** box_capacity</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Đoạn mã Python tính toán chi phí thuế GTGT cho đơn hàng được viết như sau:
-```python
-don_gia = 150000
-so_luong = 2
-tong_tien = don_gia * so_luong
-thue = tong_tien / 10
-```
-Kết quả thực thi thu được của biến `thue` có giá trị và kiểu dữ liệu là gì?</t>
+          <t>Khi hệ thống thanh toán Techmart Enterprise xử lý câu lệnh gán `total = base_price * quantity - discount + shipping`, luồng thực thi các phép toán trong biểu thức bên phải dấu `=` sẽ diễn ra theo thứ tự ưu tiên nào?</t>
         </is>
       </c>
       <c r="B6" s="3" t="n">
@@ -552,17 +541,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Giá trị 30000 thuộc kiểu số nguyên int.</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr"/>
+          <t>Phép cộng `+` được tính trước, tiếp theo là phép trừ `-`, cuối cùng là phép nhân `*` thực hiện từ phải sang trái.</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n"/>
       <c r="B7" s="4" t="n"/>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Giá trị 30000.0 thuộc kiểu số thực float.</t>
+          <t>Phép nhân `*` được tính trước, tiếp theo là phép trừ `-`, cuối cùng là phép cộng `+` thực hiện từ trái sang phải.</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
@@ -576,32 +565,32 @@
       <c r="B8" s="4" t="n"/>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Giá trị 30000 thuộc kiểu chuỗi ký tự str.</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr"/>
+          <t>Phép trừ `-` được tính trước, tiếp theo là phép cộng `+`, cuối cùng là phép nhân `*` thực hiện từ trái sang phải.</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n"/>
       <c r="B9" s="4" t="n"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Lỗi chương trình do không thể chia số nguyên cho số nguyên mà tạo ra số lẻ.</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr"/>
+          <t>Phép nhân `*` được tính trước, tiếp theo là phép cộng `+`, cuối cùng là phép trừ `-` thực hiện từ phải sang trái.</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Phần mềm quản lý đơn hàng thực hiện chia đều 83 vật phẩm vào các thùng chứa, mỗi thùng tối đa 10 vật phẩm bằng đoạn mã:
+          <t>Cho đoạn mã xử lý cập nhật tổng số tiền thanh toán đơn hàng tại Techmart Enterprise như sau:
 ```python
-tong_sp = 83
-suc_chua = 10
-so_thung = tong_sp // suc_chua
-sp_du = tong_sp % suc_chua
-```
-Giá trị của `so_thung` và `sp_du` lần lượt là bao nhiêu?</t>
+total_payment = 500000
+total_payment *= 2
+total_payment -= 100000
+total_payment += 50000
+```python
+Giá trị cuối cùng của biến `total_payment` sau khi hoàn tất đoạn mã trên là bao nhiêu?</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
@@ -609,27 +598,27 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>so_thung = 8.3 và sp_du = 3</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr"/>
+          <t>1050000</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n"/>
       <c r="B11" s="4" t="n"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>so_thung = 8 và sp_du = 0.3</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr"/>
+          <t>900000</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n"/>
       <c r="B12" s="4" t="n"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>so_thung = 8 và sp_du = 3</t>
+          <t>950000</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -643,20 +632,15 @@
       <c r="B13" s="4" t="n"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>so_thung = 3 và sp_du = 8</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr"/>
+          <t>1000000</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Giả sử số dư tài khoản giao dịch của một cửa hàng được xử lý bằng đoạn mã dưới đây:
-```python
-tai_khoan = 200
-tai_khoan += 100 * 2 ** 2 - 40 / 4
-```
-Giá trị cuối cùng của biến `tai_khoan` sau khi thực hiện xong câu lệnh trên là bao nhiêu?</t>
+          <t>Trong hệ thống Techmart Enterprise, lập trình viên cần phân biệt kết quả giữa toán tử chia số thực `/` và toán tử chia lấy phần nguyên `//`. Phát biểu nào sau đây phản ánh đúng sự khác biệt về kiểu dữ liệu và cách hoạt động của hai toán tử này?</t>
         </is>
       </c>
       <c r="B14" s="3" t="n">
@@ -664,37 +648,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1190.0 do thực hiện các phép tính lần lượt từ trái sang phải.</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr"/>
+          <t>Toán tử `/` trả về số nguyên `int` làm tròn, còn toán tử `//` luôn trả về số thực `float` có phần thập phân.</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n"/>
       <c r="B15" s="4" t="n"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>590 và giữ nguyên kiểu số nguyên int do không chứa biến float.</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr"/>
+          <t>Toán tử `/` chỉ áp dụng cho số nguyên, còn toán tử `//` bắt buộc phải áp dụng cho số thực `float` trong biểu thức.</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n"/>
       <c r="B16" s="4" t="n"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>400.0 do phép nhân và chia bị triệt tiêu bởi phép cộng trừ.</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr"/>
+          <t>Toán tử `/` trả về số thực `float` làm tròn lên, còn toán tử `//` trả về số nguyên `int` làm tròn lên.</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n"/>
       <c r="B17" s="4" t="n"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>590.0 do quy tắc ưu tiên: lũy thừa trước, nhân chia tiếp theo, cộng trừ sau cùng.</t>
+          <t>Toán tử `/` luôn trả về kiểu số thực `float`, trong khi toán tử `//` bỏ qua phần thập phân và trả về kết quả số nguyên `int` (khi hai toán hạng là số nguyên).</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
@@ -702,6 +686,63 @@
           <t>TRUE</t>
         </is>
       </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Lập trình viên viết đoạn mã tính tổng tiền sau chiết khấu cho đơn hàng Techmart Enterprise như sau:
+```python
+price = 500000
+quantity = 3
+discount = 0.1
+total = price * quantity - discount
+```python
+Đoạn mã trên gặp lỗi bẫy logic nào khiến giá trị `total` nhận kết quả là `1499999.9` thay vì `1350000.0` như kỳ vọng?</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Thiếu dấu ngoặc đơn để nhóm biểu thức tỷ lệ còn lại `(1 - discount)`, dẫn đến việc lấy tổng tiền hàng trừ trực tiếp giá trị số thực `0.1` thay vì giảm `10%`.</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n"/>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Phép nhân `price * quantity` bị lỗi kiểu dữ liệu do biến `discount` mang kiểu số thực `float` đứng ở vị trí cuối biểu thức toán học.</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n"/>
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Toán tử `-` không thể thực hiện phép tính giữa một kết quả phép nhân kiểu số nguyên `int` và một biến kiểu số thực `float` trong Python.</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n"/>
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Ngôn ngữ Python tự động thay đổi thứ tự ưu tiên, thực hiện phép trừ `quantity - discount` trước phép nhân `price * quantity`.</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
